--- a/artfynd/A 38185-2024 artfynd.xlsx
+++ b/artfynd/A 38185-2024 artfynd.xlsx
@@ -2497,10 +2497,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119840005</v>
+        <v>119839467</v>
       </c>
       <c r="B19" t="n">
-        <v>79642</v>
+        <v>97907</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2509,41 +2509,45 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>563121</v>
+        <v>563127</v>
       </c>
       <c r="R19" t="n">
-        <v>7061221</v>
+        <v>7061031</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2570,9 +2574,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2587,22 +2601,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119839467</v>
+        <v>119840005</v>
       </c>
       <c r="B20" t="n">
-        <v>97907</v>
+        <v>79642</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2611,45 +2625,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>563127</v>
+        <v>563121</v>
       </c>
       <c r="R20" t="n">
-        <v>7061031</v>
+        <v>7061221</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2676,19 +2686,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>18:40</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>18:40</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2703,12 +2703,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2919,7 +2919,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119839750</v>
+        <v>119839436</v>
       </c>
       <c r="B23" t="n">
         <v>78526</v>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>563142</v>
+        <v>563131</v>
       </c>
       <c r="R23" t="n">
-        <v>7061132</v>
+        <v>7061038</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3031,10 +3031,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119839436</v>
+        <v>119839346</v>
       </c>
       <c r="B24" t="n">
-        <v>78526</v>
+        <v>79636</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3043,25 +3043,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>563131</v>
+        <v>563107</v>
       </c>
       <c r="R24" t="n">
-        <v>7061038</v>
+        <v>7061023</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3106,7 +3106,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3143,10 +3143,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119839346</v>
+        <v>119839750</v>
       </c>
       <c r="B25" t="n">
-        <v>79636</v>
+        <v>78526</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3155,25 +3155,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3183,10 +3183,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>563107</v>
+        <v>563142</v>
       </c>
       <c r="R25" t="n">
-        <v>7061023</v>
+        <v>7061132</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3218,7 +3218,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 38185-2024 artfynd.xlsx
+++ b/artfynd/A 38185-2024 artfynd.xlsx
@@ -2497,10 +2497,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119839467</v>
+        <v>119840005</v>
       </c>
       <c r="B19" t="n">
-        <v>97907</v>
+        <v>79642</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2509,45 +2509,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>563127</v>
+        <v>563121</v>
       </c>
       <c r="R19" t="n">
-        <v>7061031</v>
+        <v>7061221</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2574,19 +2570,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>18:40</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>18:40</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2601,22 +2587,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119840005</v>
+        <v>119839467</v>
       </c>
       <c r="B20" t="n">
-        <v>79642</v>
+        <v>97907</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2625,41 +2611,45 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>563121</v>
+        <v>563127</v>
       </c>
       <c r="R20" t="n">
-        <v>7061221</v>
+        <v>7061031</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2686,9 +2676,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2703,12 +2703,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 38185-2024 artfynd.xlsx
+++ b/artfynd/A 38185-2024 artfynd.xlsx
@@ -1432,10 +1432,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119840180</v>
+        <v>119839438</v>
       </c>
       <c r="B9" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1448,37 +1448,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563031</v>
+        <v>563107</v>
       </c>
       <c r="R9" t="n">
-        <v>7061307</v>
+        <v>7061010</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1505,19 +1505,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>19:08</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>19:08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1532,19 +1522,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119839272</v>
+        <v>119840180</v>
       </c>
       <c r="B10" t="n">
         <v>78526</v>
@@ -1584,10 +1574,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563107</v>
+        <v>563031</v>
       </c>
       <c r="R10" t="n">
-        <v>7061023</v>
+        <v>7061307</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1619,7 +1609,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1629,7 +1619,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1656,10 +1646,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119839765</v>
+        <v>119840035</v>
       </c>
       <c r="B11" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1672,21 +1662,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1696,10 +1686,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563109</v>
+        <v>563084</v>
       </c>
       <c r="R11" t="n">
-        <v>7061135</v>
+        <v>7061225</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1732,11 +1722,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1763,10 +1748,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119839454</v>
+        <v>119839998</v>
       </c>
       <c r="B12" t="n">
-        <v>79642</v>
+        <v>79607</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1775,25 +1760,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1803,13 +1788,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563112</v>
+        <v>563117</v>
       </c>
       <c r="R12" t="n">
-        <v>7061002</v>
+        <v>7061221</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1865,10 +1850,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119839817</v>
+        <v>119840005</v>
       </c>
       <c r="B13" t="n">
-        <v>79607</v>
+        <v>79642</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1877,25 +1862,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1905,13 +1890,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563119</v>
+        <v>563121</v>
       </c>
       <c r="R13" t="n">
-        <v>7061134</v>
+        <v>7061221</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1967,10 +1952,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119839438</v>
+        <v>119839272</v>
       </c>
       <c r="B14" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1983,37 +1968,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
         <v>563107</v>
       </c>
       <c r="R14" t="n">
-        <v>7061010</v>
+        <v>7061023</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2040,9 +2025,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>18:33</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2057,22 +2052,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119839492</v>
+        <v>119839788</v>
       </c>
       <c r="B15" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2085,21 +2080,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2109,10 +2104,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563115</v>
+        <v>563157</v>
       </c>
       <c r="R15" t="n">
-        <v>7061068</v>
+        <v>7061169</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2145,11 +2140,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2278,10 +2268,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119840075</v>
+        <v>119839750</v>
       </c>
       <c r="B17" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2294,21 +2284,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2318,10 +2308,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>563082</v>
+        <v>563142</v>
       </c>
       <c r="R17" t="n">
-        <v>7061251</v>
+        <v>7061132</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2353,7 +2343,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2363,12 +2353,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>19:04</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2497,10 +2482,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119840005</v>
+        <v>119839817</v>
       </c>
       <c r="B19" t="n">
-        <v>79642</v>
+        <v>79607</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2509,25 +2494,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2537,13 +2522,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>563121</v>
+        <v>563119</v>
       </c>
       <c r="R19" t="n">
-        <v>7061221</v>
+        <v>7061134</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2599,10 +2584,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119839467</v>
+        <v>119839446</v>
       </c>
       <c r="B20" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2611,42 +2596,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>563127</v>
+        <v>563109</v>
       </c>
       <c r="R20" t="n">
-        <v>7061031</v>
+        <v>7061011</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2676,19 +2657,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>18:40</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>18:40</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2703,22 +2674,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119840078</v>
+        <v>119839467</v>
       </c>
       <c r="B21" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2727,38 +2698,42 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>563078</v>
+        <v>563127</v>
       </c>
       <c r="R21" t="n">
-        <v>7061270</v>
+        <v>7061031</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2788,9 +2763,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2805,19 +2790,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119840035</v>
+        <v>119840078</v>
       </c>
       <c r="B22" t="n">
         <v>79607</v>
@@ -2857,13 +2842,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>563084</v>
+        <v>563078</v>
       </c>
       <c r="R22" t="n">
-        <v>7061225</v>
+        <v>7061270</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2919,10 +2904,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119839436</v>
+        <v>119840075</v>
       </c>
       <c r="B23" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2935,21 +2920,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2959,10 +2944,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>563131</v>
+        <v>563082</v>
       </c>
       <c r="R23" t="n">
-        <v>7061038</v>
+        <v>7061251</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2994,7 +2979,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3004,7 +2989,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>19:04</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3031,10 +3021,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119839346</v>
+        <v>119839492</v>
       </c>
       <c r="B24" t="n">
-        <v>79636</v>
+        <v>57310</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3043,41 +3033,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>563107</v>
+        <v>563115</v>
       </c>
       <c r="R24" t="n">
-        <v>7061023</v>
+        <v>7061068</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3104,19 +3094,14 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>18:35</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>18:35</t>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3131,19 +3116,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119839750</v>
+        <v>119839765</v>
       </c>
       <c r="B25" t="n">
         <v>78526</v>
@@ -3179,17 +3164,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>563142</v>
+        <v>563109</v>
       </c>
       <c r="R25" t="n">
-        <v>7061132</v>
+        <v>7061135</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3216,19 +3201,14 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>18:48</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>18:48</t>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3243,19 +3223,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119839763</v>
+        <v>119839930</v>
       </c>
       <c r="B26" t="n">
         <v>78526</v>
@@ -3291,17 +3271,17 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>563149</v>
+        <v>563131</v>
       </c>
       <c r="R26" t="n">
-        <v>7061158</v>
+        <v>7061213</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3328,9 +3308,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>18:57</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3345,22 +3335,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119839446</v>
+        <v>119839454</v>
       </c>
       <c r="B27" t="n">
-        <v>79607</v>
+        <v>79642</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3369,25 +3359,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3397,10 +3387,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>563109</v>
+        <v>563112</v>
       </c>
       <c r="R27" t="n">
-        <v>7061011</v>
+        <v>7061002</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3576,7 +3566,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119839930</v>
+        <v>119839436</v>
       </c>
       <c r="B29" t="n">
         <v>78526</v>
@@ -3619,7 +3609,7 @@
         <v>563131</v>
       </c>
       <c r="R29" t="n">
-        <v>7061213</v>
+        <v>7061038</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3651,7 +3641,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3661,7 +3651,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3688,10 +3678,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119839788</v>
+        <v>119839763</v>
       </c>
       <c r="B30" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3704,21 +3694,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3728,10 +3718,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>563157</v>
+        <v>563149</v>
       </c>
       <c r="R30" t="n">
-        <v>7061169</v>
+        <v>7061158</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3790,10 +3780,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119839998</v>
+        <v>119839346</v>
       </c>
       <c r="B31" t="n">
-        <v>79607</v>
+        <v>79636</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3802,41 +3792,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>563117</v>
+        <v>563107</v>
       </c>
       <c r="R31" t="n">
-        <v>7061221</v>
+        <v>7061023</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3863,9 +3853,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3880,12 +3880,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>

--- a/artfynd/A 38185-2024 artfynd.xlsx
+++ b/artfynd/A 38185-2024 artfynd.xlsx
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119839630</v>
+        <v>119839438</v>
       </c>
       <c r="B8" t="n">
-        <v>57463</v>
+        <v>79608</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,46 +1327,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563124</v>
+        <v>563107</v>
       </c>
       <c r="R8" t="n">
-        <v>7061062</v>
+        <v>7061010</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1393,19 +1384,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>18:44</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>18:44</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1420,22 +1401,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119839438</v>
+        <v>119840180</v>
       </c>
       <c r="B9" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1448,37 +1429,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563107</v>
+        <v>563031</v>
       </c>
       <c r="R9" t="n">
-        <v>7061010</v>
+        <v>7061307</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1505,9 +1486,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>19:08</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1522,22 +1513,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119840180</v>
+        <v>119839630</v>
       </c>
       <c r="B10" t="n">
-        <v>78526</v>
+        <v>57463</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1550,34 +1541,43 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563031</v>
+        <v>563124</v>
       </c>
       <c r="R10" t="n">
-        <v>7061307</v>
+        <v>7061062</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2584,10 +2584,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119839446</v>
+        <v>119839467</v>
       </c>
       <c r="B20" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2596,38 +2596,42 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>563109</v>
+        <v>563127</v>
       </c>
       <c r="R20" t="n">
-        <v>7061011</v>
+        <v>7061031</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2657,9 +2661,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2674,22 +2688,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119839467</v>
+        <v>119839446</v>
       </c>
       <c r="B21" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2698,42 +2712,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>563127</v>
+        <v>563109</v>
       </c>
       <c r="R21" t="n">
-        <v>7061031</v>
+        <v>7061011</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2763,19 +2773,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>18:40</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>18:40</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2790,12 +2790,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2904,10 +2904,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119840075</v>
+        <v>119839765</v>
       </c>
       <c r="B23" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2920,37 +2920,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>563082</v>
+        <v>563109</v>
       </c>
       <c r="R23" t="n">
-        <v>7061251</v>
+        <v>7061135</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2977,24 +2977,14 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>19:04</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>19:04</t>
-        </is>
-      </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3009,19 +2999,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119839492</v>
+        <v>119840075</v>
       </c>
       <c r="B24" t="n">
         <v>57310</v>
@@ -3057,17 +3047,17 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>563115</v>
+        <v>563082</v>
       </c>
       <c r="R24" t="n">
-        <v>7061068</v>
+        <v>7061251</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3094,9 +3084,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>19:04</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3116,22 +3116,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119839765</v>
+        <v>119839492</v>
       </c>
       <c r="B25" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3144,21 +3144,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>563109</v>
+        <v>563115</v>
       </c>
       <c r="R25" t="n">
-        <v>7061135</v>
+        <v>7061068</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3223,12 +3223,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3678,10 +3678,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119839763</v>
+        <v>119839346</v>
       </c>
       <c r="B30" t="n">
-        <v>78526</v>
+        <v>79636</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3690,41 +3690,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>563149</v>
+        <v>563107</v>
       </c>
       <c r="R30" t="n">
-        <v>7061158</v>
+        <v>7061023</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3751,9 +3751,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3768,22 +3778,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119839346</v>
+        <v>119839763</v>
       </c>
       <c r="B31" t="n">
-        <v>79636</v>
+        <v>78526</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3792,41 +3802,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>563107</v>
+        <v>563149</v>
       </c>
       <c r="R31" t="n">
-        <v>7061023</v>
+        <v>7061158</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3853,19 +3863,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>18:35</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>18:35</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3880,12 +3880,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>

--- a/artfynd/A 38185-2024 artfynd.xlsx
+++ b/artfynd/A 38185-2024 artfynd.xlsx
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119839438</v>
+        <v>119840075</v>
       </c>
       <c r="B8" t="n">
-        <v>79608</v>
+        <v>57310</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,37 +1327,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563107</v>
+        <v>563082</v>
       </c>
       <c r="R8" t="n">
-        <v>7061010</v>
+        <v>7061251</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1384,9 +1384,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>19:04</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>19:04</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1401,22 +1416,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119840180</v>
+        <v>119839467</v>
       </c>
       <c r="B9" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,38 +1440,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563031</v>
+        <v>563127</v>
       </c>
       <c r="R9" t="n">
-        <v>7061307</v>
+        <v>7061031</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1488,7 +1507,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1498,7 +1517,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1525,10 +1544,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119839630</v>
+        <v>119839446</v>
       </c>
       <c r="B10" t="n">
-        <v>57463</v>
+        <v>79607</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1541,43 +1560,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563124</v>
+        <v>563109</v>
       </c>
       <c r="R10" t="n">
-        <v>7061062</v>
+        <v>7061011</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1607,19 +1617,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>18:44</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>18:44</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1634,22 +1634,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119840035</v>
+        <v>119839346</v>
       </c>
       <c r="B11" t="n">
-        <v>79607</v>
+        <v>79636</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1658,41 +1658,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563084</v>
+        <v>563107</v>
       </c>
       <c r="R11" t="n">
-        <v>7061225</v>
+        <v>7061023</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1719,9 +1719,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1736,22 +1746,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119839998</v>
+        <v>119839750</v>
       </c>
       <c r="B12" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1764,37 +1774,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563117</v>
+        <v>563142</v>
       </c>
       <c r="R12" t="n">
-        <v>7061221</v>
+        <v>7061132</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1821,9 +1831,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>18:48</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1838,22 +1858,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119840005</v>
+        <v>119840152</v>
       </c>
       <c r="B13" t="n">
-        <v>79642</v>
+        <v>57310</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1862,41 +1882,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563121</v>
+        <v>563083</v>
       </c>
       <c r="R13" t="n">
-        <v>7061221</v>
+        <v>7061265</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1923,9 +1943,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1940,19 +1975,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119839272</v>
+        <v>119839763</v>
       </c>
       <c r="B14" t="n">
         <v>78526</v>
@@ -1988,17 +2023,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>563107</v>
+        <v>563149</v>
       </c>
       <c r="R14" t="n">
-        <v>7061023</v>
+        <v>7061158</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2025,19 +2060,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>18:33</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>18:33</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2052,22 +2077,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119839788</v>
+        <v>119839436</v>
       </c>
       <c r="B15" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2080,37 +2105,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563157</v>
+        <v>563131</v>
       </c>
       <c r="R15" t="n">
-        <v>7061169</v>
+        <v>7061038</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2137,9 +2162,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>18:38</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2154,22 +2189,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119839461</v>
+        <v>119840078</v>
       </c>
       <c r="B16" t="n">
-        <v>79643</v>
+        <v>79607</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2178,25 +2213,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2206,10 +2241,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>563111</v>
+        <v>563078</v>
       </c>
       <c r="R16" t="n">
-        <v>7061002</v>
+        <v>7061270</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2268,10 +2303,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119839750</v>
+        <v>119840005</v>
       </c>
       <c r="B17" t="n">
-        <v>78526</v>
+        <v>79642</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2280,20 +2315,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2304,17 +2339,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>563142</v>
+        <v>563121</v>
       </c>
       <c r="R17" t="n">
-        <v>7061132</v>
+        <v>7061221</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2341,19 +2376,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>18:48</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>18:48</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2368,22 +2393,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119839784</v>
+        <v>119839461</v>
       </c>
       <c r="B18" t="n">
-        <v>79607</v>
+        <v>79643</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2392,25 +2417,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2420,10 +2445,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>563118</v>
+        <v>563111</v>
       </c>
       <c r="R18" t="n">
-        <v>7061145</v>
+        <v>7061002</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2482,10 +2507,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119839817</v>
+        <v>119839272</v>
       </c>
       <c r="B19" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2498,37 +2523,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>563119</v>
+        <v>563107</v>
       </c>
       <c r="R19" t="n">
-        <v>7061134</v>
+        <v>7061023</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2555,9 +2580,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>18:33</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2572,22 +2607,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119839467</v>
+        <v>119839454</v>
       </c>
       <c r="B20" t="n">
-        <v>97907</v>
+        <v>79642</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2596,42 +2631,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>563127</v>
+        <v>563112</v>
       </c>
       <c r="R20" t="n">
-        <v>7061031</v>
+        <v>7061002</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2661,19 +2692,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>18:40</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>18:40</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2688,22 +2709,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119839446</v>
+        <v>119839765</v>
       </c>
       <c r="B21" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2716,21 +2737,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2743,10 +2764,10 @@
         <v>563109</v>
       </c>
       <c r="R21" t="n">
-        <v>7061011</v>
+        <v>7061135</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2776,6 +2797,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2802,7 +2828,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119840078</v>
+        <v>119839788</v>
       </c>
       <c r="B22" t="n">
         <v>79607</v>
@@ -2842,13 +2868,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>563078</v>
+        <v>563157</v>
       </c>
       <c r="R22" t="n">
-        <v>7061270</v>
+        <v>7061169</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2892,22 +2918,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119839765</v>
+        <v>119839784</v>
       </c>
       <c r="B23" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2920,21 +2946,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2944,13 +2970,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>563109</v>
+        <v>563118</v>
       </c>
       <c r="R23" t="n">
-        <v>7061135</v>
+        <v>7061145</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2980,11 +3006,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3011,7 +3032,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119840075</v>
+        <v>119839492</v>
       </c>
       <c r="B24" t="n">
         <v>57310</v>
@@ -3047,17 +3068,17 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>563082</v>
+        <v>563115</v>
       </c>
       <c r="R24" t="n">
-        <v>7061251</v>
+        <v>7061068</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3084,19 +3105,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>19:04</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>19:04</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3116,22 +3127,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119839492</v>
+        <v>119839930</v>
       </c>
       <c r="B25" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3144,37 +3155,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>563115</v>
+        <v>563131</v>
       </c>
       <c r="R25" t="n">
-        <v>7061068</v>
+        <v>7061213</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3201,14 +3212,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>18:57</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3223,22 +3239,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119839930</v>
+        <v>119840035</v>
       </c>
       <c r="B26" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3251,37 +3267,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>563131</v>
+        <v>563084</v>
       </c>
       <c r="R26" t="n">
-        <v>7061213</v>
+        <v>7061225</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3308,19 +3324,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>18:57</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>18:57</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3335,22 +3341,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119839454</v>
+        <v>119840180</v>
       </c>
       <c r="B27" t="n">
-        <v>79642</v>
+        <v>78526</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3359,20 +3365,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3383,14 +3389,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>563112</v>
+        <v>563031</v>
       </c>
       <c r="R27" t="n">
-        <v>7061002</v>
+        <v>7061307</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,9 +3426,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>19:08</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3437,22 +3453,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119840152</v>
+        <v>119839817</v>
       </c>
       <c r="B28" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3465,37 +3481,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>563083</v>
+        <v>563119</v>
       </c>
       <c r="R28" t="n">
-        <v>7061265</v>
+        <v>7061134</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3522,24 +3538,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>19:05</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>19:05</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3554,22 +3555,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119839436</v>
+        <v>119839998</v>
       </c>
       <c r="B29" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3582,37 +3583,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>563131</v>
+        <v>563117</v>
       </c>
       <c r="R29" t="n">
-        <v>7061038</v>
+        <v>7061221</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3639,19 +3640,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>18:38</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>18:38</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3666,22 +3657,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119839346</v>
+        <v>119839630</v>
       </c>
       <c r="B30" t="n">
-        <v>79636</v>
+        <v>57463</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3690,38 +3681,47 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>563107</v>
+        <v>563124</v>
       </c>
       <c r="R30" t="n">
-        <v>7061023</v>
+        <v>7061062</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3753,7 +3753,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3790,10 +3790,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119839763</v>
+        <v>119839438</v>
       </c>
       <c r="B31" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3806,21 +3806,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3830,10 +3830,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>563149</v>
+        <v>563107</v>
       </c>
       <c r="R31" t="n">
-        <v>7061158</v>
+        <v>7061010</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3880,12 +3880,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>

--- a/artfynd/A 38185-2024 artfynd.xlsx
+++ b/artfynd/A 38185-2024 artfynd.xlsx
@@ -1544,10 +1544,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119839446</v>
+        <v>119839346</v>
       </c>
       <c r="B10" t="n">
-        <v>79607</v>
+        <v>79636</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1556,38 +1556,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563109</v>
+        <v>563107</v>
       </c>
       <c r="R10" t="n">
-        <v>7061011</v>
+        <v>7061023</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1617,9 +1617,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1634,22 +1644,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119839346</v>
+        <v>119839446</v>
       </c>
       <c r="B11" t="n">
-        <v>79636</v>
+        <v>79607</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1658,38 +1668,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563107</v>
+        <v>563109</v>
       </c>
       <c r="R11" t="n">
-        <v>7061023</v>
+        <v>7061011</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1719,19 +1729,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>18:35</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>18:35</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1746,12 +1746,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -2930,10 +2930,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119839784</v>
+        <v>119839492</v>
       </c>
       <c r="B23" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2946,21 +2946,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2970,13 +2970,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>563118</v>
+        <v>563115</v>
       </c>
       <c r="R23" t="n">
-        <v>7061145</v>
+        <v>7061068</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3006,6 +3006,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3020,22 +3025,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119839492</v>
+        <v>119839784</v>
       </c>
       <c r="B24" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3048,21 +3053,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3072,13 +3077,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>563115</v>
+        <v>563118</v>
       </c>
       <c r="R24" t="n">
-        <v>7061068</v>
+        <v>7061145</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3108,11 +3113,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3127,12 +3127,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 38185-2024 artfynd.xlsx
+++ b/artfynd/A 38185-2024 artfynd.xlsx
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119840075</v>
+        <v>119839630</v>
       </c>
       <c r="B8" t="n">
-        <v>57310</v>
+        <v>57463</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,34 +1327,43 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563082</v>
+        <v>563124</v>
       </c>
       <c r="R8" t="n">
-        <v>7061251</v>
+        <v>7061062</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1386,7 +1395,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1396,12 +1405,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>19:04</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1428,10 +1432,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119839467</v>
+        <v>119839346</v>
       </c>
       <c r="B9" t="n">
-        <v>97907</v>
+        <v>79636</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1440,42 +1444,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563127</v>
+        <v>563107</v>
       </c>
       <c r="R9" t="n">
-        <v>7061031</v>
+        <v>7061023</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1544,10 +1544,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119839346</v>
+        <v>119839272</v>
       </c>
       <c r="B10" t="n">
-        <v>79636</v>
+        <v>78526</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1556,25 +1556,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1619,7 +1619,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1656,7 +1656,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119839446</v>
+        <v>119840078</v>
       </c>
       <c r="B11" t="n">
         <v>79607</v>
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563109</v>
+        <v>563078</v>
       </c>
       <c r="R11" t="n">
-        <v>7061011</v>
+        <v>7061270</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1758,7 +1758,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119839750</v>
+        <v>119839436</v>
       </c>
       <c r="B12" t="n">
         <v>78526</v>
@@ -1798,10 +1798,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563142</v>
+        <v>563131</v>
       </c>
       <c r="R12" t="n">
-        <v>7061132</v>
+        <v>7061038</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1870,10 +1870,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119840152</v>
+        <v>119840035</v>
       </c>
       <c r="B13" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1886,37 +1886,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563083</v>
+        <v>563084</v>
       </c>
       <c r="R13" t="n">
-        <v>7061265</v>
+        <v>7061225</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1943,24 +1943,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>19:05</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>19:05</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1975,22 +1960,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119839763</v>
+        <v>119839998</v>
       </c>
       <c r="B14" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2003,21 +1988,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2027,10 +2012,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>563149</v>
+        <v>563117</v>
       </c>
       <c r="R14" t="n">
-        <v>7061158</v>
+        <v>7061221</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2077,22 +2062,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119839436</v>
+        <v>119839492</v>
       </c>
       <c r="B15" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2105,37 +2090,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563131</v>
+        <v>563115</v>
       </c>
       <c r="R15" t="n">
-        <v>7061038</v>
+        <v>7061068</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2162,19 +2147,14 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>18:38</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>18:38</t>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2189,22 +2169,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119840078</v>
+        <v>119840180</v>
       </c>
       <c r="B16" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2217,34 +2197,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>563078</v>
+        <v>563031</v>
       </c>
       <c r="R16" t="n">
-        <v>7061270</v>
+        <v>7061307</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2274,9 +2254,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>19:08</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2291,22 +2281,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119840005</v>
+        <v>119839750</v>
       </c>
       <c r="B17" t="n">
-        <v>79642</v>
+        <v>78526</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2315,20 +2305,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2339,17 +2329,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>563121</v>
+        <v>563142</v>
       </c>
       <c r="R17" t="n">
-        <v>7061221</v>
+        <v>7061132</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2376,9 +2366,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>18:48</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2393,12 +2393,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2507,10 +2507,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119839272</v>
+        <v>119840005</v>
       </c>
       <c r="B19" t="n">
-        <v>78526</v>
+        <v>79642</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2519,20 +2519,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2543,17 +2543,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>563107</v>
+        <v>563121</v>
       </c>
       <c r="R19" t="n">
-        <v>7061023</v>
+        <v>7061221</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2580,19 +2580,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>18:33</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>18:33</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2607,22 +2597,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119839454</v>
+        <v>119839438</v>
       </c>
       <c r="B20" t="n">
-        <v>79642</v>
+        <v>79608</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2631,25 +2621,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2659,13 +2649,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>563112</v>
+        <v>563107</v>
       </c>
       <c r="R20" t="n">
-        <v>7061002</v>
+        <v>7061010</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2721,10 +2711,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119839765</v>
+        <v>119840152</v>
       </c>
       <c r="B21" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2737,37 +2727,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>563109</v>
+        <v>563083</v>
       </c>
       <c r="R21" t="n">
-        <v>7061135</v>
+        <v>7061265</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2794,14 +2784,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2816,12 +2816,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2930,10 +2930,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119839492</v>
+        <v>119839467</v>
       </c>
       <c r="B23" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2942,41 +2942,45 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>563115</v>
+        <v>563127</v>
       </c>
       <c r="R23" t="n">
-        <v>7061068</v>
+        <v>7061031</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3003,14 +3007,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3025,12 +3034,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3139,10 +3148,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119839930</v>
+        <v>119839446</v>
       </c>
       <c r="B25" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3155,34 +3164,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>563131</v>
+        <v>563109</v>
       </c>
       <c r="R25" t="n">
-        <v>7061213</v>
+        <v>7061011</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3212,19 +3221,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>18:57</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>18:57</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3239,22 +3238,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119840035</v>
+        <v>119839454</v>
       </c>
       <c r="B26" t="n">
-        <v>79607</v>
+        <v>79642</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3263,25 +3262,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3291,13 +3290,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>563084</v>
+        <v>563112</v>
       </c>
       <c r="R26" t="n">
-        <v>7061225</v>
+        <v>7061002</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3353,7 +3352,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119840180</v>
+        <v>119839763</v>
       </c>
       <c r="B27" t="n">
         <v>78526</v>
@@ -3389,17 +3388,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>563031</v>
+        <v>563149</v>
       </c>
       <c r="R27" t="n">
-        <v>7061307</v>
+        <v>7061158</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3426,19 +3425,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>19:08</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>19:08</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3453,12 +3442,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3567,10 +3556,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119839998</v>
+        <v>119839930</v>
       </c>
       <c r="B29" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3583,37 +3572,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>563117</v>
+        <v>563131</v>
       </c>
       <c r="R29" t="n">
-        <v>7061221</v>
+        <v>7061213</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3640,9 +3629,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>18:57</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3657,22 +3656,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119839630</v>
+        <v>119840075</v>
       </c>
       <c r="B30" t="n">
-        <v>57463</v>
+        <v>57310</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3685,43 +3684,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>563124</v>
+        <v>563082</v>
       </c>
       <c r="R30" t="n">
-        <v>7061062</v>
+        <v>7061251</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3753,7 +3743,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3763,7 +3753,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>19:04</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3790,10 +3785,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119839438</v>
+        <v>119839765</v>
       </c>
       <c r="B31" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3806,21 +3801,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3830,10 +3825,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>563107</v>
+        <v>563109</v>
       </c>
       <c r="R31" t="n">
-        <v>7061010</v>
+        <v>7061135</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3866,6 +3861,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 38185-2024 artfynd.xlsx
+++ b/artfynd/A 38185-2024 artfynd.xlsx
@@ -1972,10 +1972,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119839998</v>
+        <v>119839492</v>
       </c>
       <c r="B14" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1988,21 +1988,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2012,10 +2012,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>563117</v>
+        <v>563115</v>
       </c>
       <c r="R14" t="n">
-        <v>7061221</v>
+        <v>7061068</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2050,6 +2050,11 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2062,22 +2067,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119839492</v>
+        <v>119839998</v>
       </c>
       <c r="B15" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2090,21 +2095,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2114,10 +2119,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563115</v>
+        <v>563117</v>
       </c>
       <c r="R15" t="n">
-        <v>7061068</v>
+        <v>7061221</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2152,11 +2157,6 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2169,12 +2169,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2507,10 +2507,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119840005</v>
+        <v>119839438</v>
       </c>
       <c r="B19" t="n">
-        <v>79642</v>
+        <v>79608</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2519,25 +2519,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2547,10 +2547,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>563121</v>
+        <v>563107</v>
       </c>
       <c r="R19" t="n">
-        <v>7061221</v>
+        <v>7061010</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2609,10 +2609,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119839438</v>
+        <v>119840005</v>
       </c>
       <c r="B20" t="n">
-        <v>79608</v>
+        <v>79642</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2621,25 +2621,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2649,10 +2649,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>563107</v>
+        <v>563121</v>
       </c>
       <c r="R20" t="n">
-        <v>7061010</v>
+        <v>7061221</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -3454,10 +3454,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119839817</v>
+        <v>119839930</v>
       </c>
       <c r="B28" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3470,37 +3470,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>563119</v>
+        <v>563131</v>
       </c>
       <c r="R28" t="n">
-        <v>7061134</v>
+        <v>7061213</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3527,9 +3527,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>18:57</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3544,22 +3554,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119839930</v>
+        <v>119839817</v>
       </c>
       <c r="B29" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3572,37 +3582,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>563131</v>
+        <v>563119</v>
       </c>
       <c r="R29" t="n">
-        <v>7061213</v>
+        <v>7061134</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3629,19 +3639,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>18:57</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>18:57</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3656,12 +3656,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>

--- a/artfynd/A 38185-2024 artfynd.xlsx
+++ b/artfynd/A 38185-2024 artfynd.xlsx
@@ -1972,10 +1972,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119839492</v>
+        <v>119839998</v>
       </c>
       <c r="B14" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1988,21 +1988,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2012,10 +2012,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>563115</v>
+        <v>563117</v>
       </c>
       <c r="R14" t="n">
-        <v>7061068</v>
+        <v>7061221</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2050,11 +2050,6 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2067,22 +2062,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119839998</v>
+        <v>119839492</v>
       </c>
       <c r="B15" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2095,21 +2090,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2119,10 +2114,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563117</v>
+        <v>563115</v>
       </c>
       <c r="R15" t="n">
-        <v>7061221</v>
+        <v>7061068</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2157,6 +2152,11 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2169,12 +2169,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2507,10 +2507,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119839438</v>
+        <v>119840005</v>
       </c>
       <c r="B19" t="n">
-        <v>79608</v>
+        <v>79642</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2519,25 +2519,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2547,10 +2547,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>563107</v>
+        <v>563121</v>
       </c>
       <c r="R19" t="n">
-        <v>7061010</v>
+        <v>7061221</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2609,10 +2609,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119840005</v>
+        <v>119839438</v>
       </c>
       <c r="B20" t="n">
-        <v>79642</v>
+        <v>79608</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2621,25 +2621,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2649,10 +2649,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>563121</v>
+        <v>563107</v>
       </c>
       <c r="R20" t="n">
-        <v>7061221</v>
+        <v>7061010</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -3454,10 +3454,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119839930</v>
+        <v>119839817</v>
       </c>
       <c r="B28" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3470,37 +3470,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>563131</v>
+        <v>563119</v>
       </c>
       <c r="R28" t="n">
-        <v>7061213</v>
+        <v>7061134</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3527,19 +3527,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>18:57</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>18:57</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3554,22 +3544,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119839817</v>
+        <v>119839930</v>
       </c>
       <c r="B29" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3582,37 +3572,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>563119</v>
+        <v>563131</v>
       </c>
       <c r="R29" t="n">
-        <v>7061134</v>
+        <v>7061213</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3639,9 +3629,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>18:57</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3656,12 +3656,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>

--- a/artfynd/A 38185-2024 artfynd.xlsx
+++ b/artfynd/A 38185-2024 artfynd.xlsx
@@ -1972,10 +1972,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119839998</v>
+        <v>119839492</v>
       </c>
       <c r="B14" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1988,21 +1988,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2012,10 +2012,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>563117</v>
+        <v>563115</v>
       </c>
       <c r="R14" t="n">
-        <v>7061221</v>
+        <v>7061068</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2050,6 +2050,11 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2062,22 +2067,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119839492</v>
+        <v>119839998</v>
       </c>
       <c r="B15" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2090,21 +2095,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2114,10 +2119,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563115</v>
+        <v>563117</v>
       </c>
       <c r="R15" t="n">
-        <v>7061068</v>
+        <v>7061221</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2152,11 +2157,6 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2169,12 +2169,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -3250,10 +3250,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119839454</v>
+        <v>119839763</v>
       </c>
       <c r="B26" t="n">
-        <v>79642</v>
+        <v>78526</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3262,20 +3262,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3290,13 +3290,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>563112</v>
+        <v>563149</v>
       </c>
       <c r="R26" t="n">
-        <v>7061002</v>
+        <v>7061158</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3340,22 +3340,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119839763</v>
+        <v>119839454</v>
       </c>
       <c r="B27" t="n">
-        <v>78526</v>
+        <v>79642</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3364,20 +3364,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3392,13 +3392,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>563149</v>
+        <v>563112</v>
       </c>
       <c r="R27" t="n">
-        <v>7061158</v>
+        <v>7061002</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3442,12 +3442,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>

--- a/artfynd/A 38185-2024 artfynd.xlsx
+++ b/artfynd/A 38185-2024 artfynd.xlsx
@@ -2507,10 +2507,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119840005</v>
+        <v>119839438</v>
       </c>
       <c r="B19" t="n">
-        <v>79642</v>
+        <v>79608</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2519,25 +2519,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2547,10 +2547,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>563121</v>
+        <v>563107</v>
       </c>
       <c r="R19" t="n">
-        <v>7061221</v>
+        <v>7061010</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2609,10 +2609,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119839438</v>
+        <v>119840005</v>
       </c>
       <c r="B20" t="n">
-        <v>79608</v>
+        <v>79642</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2621,25 +2621,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2649,10 +2649,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>563107</v>
+        <v>563121</v>
       </c>
       <c r="R20" t="n">
-        <v>7061010</v>
+        <v>7061221</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -3250,10 +3250,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119839763</v>
+        <v>119839454</v>
       </c>
       <c r="B26" t="n">
-        <v>78526</v>
+        <v>79642</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3262,20 +3262,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3290,13 +3290,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>563149</v>
+        <v>563112</v>
       </c>
       <c r="R26" t="n">
-        <v>7061158</v>
+        <v>7061002</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3340,22 +3340,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119839454</v>
+        <v>119839763</v>
       </c>
       <c r="B27" t="n">
-        <v>79642</v>
+        <v>78526</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3364,20 +3364,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3392,13 +3392,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>563112</v>
+        <v>563149</v>
       </c>
       <c r="R27" t="n">
-        <v>7061002</v>
+        <v>7061158</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3442,22 +3442,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119839817</v>
+        <v>119839930</v>
       </c>
       <c r="B28" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3470,37 +3470,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>563119</v>
+        <v>563131</v>
       </c>
       <c r="R28" t="n">
-        <v>7061134</v>
+        <v>7061213</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3527,9 +3527,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>18:57</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3544,22 +3554,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119839930</v>
+        <v>119839817</v>
       </c>
       <c r="B29" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3572,37 +3582,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>563131</v>
+        <v>563119</v>
       </c>
       <c r="R29" t="n">
-        <v>7061213</v>
+        <v>7061134</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3629,19 +3639,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>18:57</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>18:57</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3656,12 +3656,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>

--- a/artfynd/A 38185-2024 artfynd.xlsx
+++ b/artfynd/A 38185-2024 artfynd.xlsx
@@ -1972,10 +1972,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119839492</v>
+        <v>119839998</v>
       </c>
       <c r="B14" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1988,21 +1988,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2012,10 +2012,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>563115</v>
+        <v>563117</v>
       </c>
       <c r="R14" t="n">
-        <v>7061068</v>
+        <v>7061221</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2050,11 +2050,6 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2067,22 +2062,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119839998</v>
+        <v>119839492</v>
       </c>
       <c r="B15" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2095,21 +2090,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2119,10 +2114,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563117</v>
+        <v>563115</v>
       </c>
       <c r="R15" t="n">
-        <v>7061221</v>
+        <v>7061068</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2157,6 +2152,11 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2169,12 +2169,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2507,10 +2507,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119839438</v>
+        <v>119840005</v>
       </c>
       <c r="B19" t="n">
-        <v>79608</v>
+        <v>79642</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2519,25 +2519,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2547,10 +2547,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>563107</v>
+        <v>563121</v>
       </c>
       <c r="R19" t="n">
-        <v>7061010</v>
+        <v>7061221</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2609,10 +2609,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119840005</v>
+        <v>119839438</v>
       </c>
       <c r="B20" t="n">
-        <v>79642</v>
+        <v>79608</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2621,25 +2621,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2649,10 +2649,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>563121</v>
+        <v>563107</v>
       </c>
       <c r="R20" t="n">
-        <v>7061221</v>
+        <v>7061010</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>

--- a/artfynd/A 38185-2024 artfynd.xlsx
+++ b/artfynd/A 38185-2024 artfynd.xlsx
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119839630</v>
+        <v>119839750</v>
       </c>
       <c r="B8" t="n">
-        <v>57463</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,43 +1327,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563124</v>
+        <v>563142</v>
       </c>
       <c r="R8" t="n">
-        <v>7061062</v>
+        <v>7061132</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1395,7 +1386,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1405,7 +1396,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119839346</v>
+        <v>119839784</v>
       </c>
       <c r="B9" t="n">
-        <v>79636</v>
+        <v>79623</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1444,38 +1435,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563107</v>
+        <v>563118</v>
       </c>
       <c r="R9" t="n">
-        <v>7061023</v>
+        <v>7061145</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1505,19 +1496,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>18:35</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>18:35</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1532,22 +1513,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119839272</v>
+        <v>119839630</v>
       </c>
       <c r="B10" t="n">
-        <v>78526</v>
+        <v>57473</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1560,34 +1541,43 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563107</v>
+        <v>563124</v>
       </c>
       <c r="R10" t="n">
-        <v>7061023</v>
+        <v>7061062</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1619,7 +1609,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1629,7 +1619,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1656,10 +1646,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119840078</v>
+        <v>119839438</v>
       </c>
       <c r="B11" t="n">
-        <v>79607</v>
+        <v>79624</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1672,21 +1662,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1696,13 +1686,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563078</v>
+        <v>563107</v>
       </c>
       <c r="R11" t="n">
-        <v>7061270</v>
+        <v>7061010</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1758,10 +1748,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119839436</v>
+        <v>119839454</v>
       </c>
       <c r="B12" t="n">
-        <v>78526</v>
+        <v>79658</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1770,20 +1760,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1794,14 +1784,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563131</v>
+        <v>563112</v>
       </c>
       <c r="R12" t="n">
-        <v>7061038</v>
+        <v>7061002</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1831,19 +1821,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>18:38</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>18:38</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1858,22 +1838,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119840035</v>
+        <v>119840005</v>
       </c>
       <c r="B13" t="n">
-        <v>79607</v>
+        <v>79658</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1882,25 +1862,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1910,10 +1890,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563084</v>
+        <v>563121</v>
       </c>
       <c r="R13" t="n">
-        <v>7061225</v>
+        <v>7061221</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1972,10 +1952,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119839998</v>
+        <v>119839930</v>
       </c>
       <c r="B14" t="n">
-        <v>79607</v>
+        <v>78542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1988,37 +1968,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>563117</v>
+        <v>563131</v>
       </c>
       <c r="R14" t="n">
-        <v>7061221</v>
+        <v>7061213</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2045,9 +2025,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>18:57</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2062,22 +2052,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119839492</v>
+        <v>119839765</v>
       </c>
       <c r="B15" t="n">
-        <v>57310</v>
+        <v>78542</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2090,21 +2080,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2114,10 +2104,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563115</v>
+        <v>563109</v>
       </c>
       <c r="R15" t="n">
-        <v>7061068</v>
+        <v>7061135</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2154,7 +2144,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2169,22 +2159,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119840180</v>
+        <v>119839492</v>
       </c>
       <c r="B16" t="n">
-        <v>78526</v>
+        <v>57320</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2197,37 +2187,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>563031</v>
+        <v>563115</v>
       </c>
       <c r="R16" t="n">
-        <v>7061307</v>
+        <v>7061068</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2254,19 +2244,14 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>19:08</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>19:08</t>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2281,22 +2266,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119839750</v>
+        <v>119839272</v>
       </c>
       <c r="B17" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2333,10 +2318,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>563142</v>
+        <v>563107</v>
       </c>
       <c r="R17" t="n">
-        <v>7061132</v>
+        <v>7061023</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2368,7 +2353,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2378,7 +2363,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2405,10 +2390,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119839461</v>
+        <v>119839446</v>
       </c>
       <c r="B18" t="n">
-        <v>79643</v>
+        <v>79623</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2417,25 +2402,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2445,10 +2430,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>563111</v>
+        <v>563109</v>
       </c>
       <c r="R18" t="n">
-        <v>7061002</v>
+        <v>7061011</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2507,10 +2492,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119840005</v>
+        <v>119840075</v>
       </c>
       <c r="B19" t="n">
-        <v>79642</v>
+        <v>57320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2519,41 +2504,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>563121</v>
+        <v>563082</v>
       </c>
       <c r="R19" t="n">
-        <v>7061221</v>
+        <v>7061251</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2580,9 +2565,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>19:04</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>19:04</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2597,22 +2597,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119839438</v>
+        <v>119840152</v>
       </c>
       <c r="B20" t="n">
-        <v>79608</v>
+        <v>57320</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2625,37 +2625,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>563107</v>
+        <v>563083</v>
       </c>
       <c r="R20" t="n">
-        <v>7061010</v>
+        <v>7061265</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2682,9 +2682,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2699,22 +2714,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119840152</v>
+        <v>119839436</v>
       </c>
       <c r="B21" t="n">
-        <v>57310</v>
+        <v>78542</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2727,21 +2742,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2751,10 +2766,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>563083</v>
+        <v>563131</v>
       </c>
       <c r="R21" t="n">
-        <v>7061265</v>
+        <v>7061038</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2786,7 +2801,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2796,12 +2811,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>19:05</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2828,10 +2838,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119839788</v>
+        <v>119840035</v>
       </c>
       <c r="B22" t="n">
-        <v>79607</v>
+        <v>79623</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2868,10 +2878,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>563157</v>
+        <v>563084</v>
       </c>
       <c r="R22" t="n">
-        <v>7061169</v>
+        <v>7061225</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2918,22 +2928,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119839467</v>
+        <v>119839788</v>
       </c>
       <c r="B23" t="n">
-        <v>97907</v>
+        <v>79623</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2942,45 +2952,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>563127</v>
+        <v>563157</v>
       </c>
       <c r="R23" t="n">
-        <v>7061031</v>
+        <v>7061169</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3007,19 +3013,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>18:40</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>18:40</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3034,22 +3030,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119839784</v>
+        <v>119839998</v>
       </c>
       <c r="B24" t="n">
-        <v>79607</v>
+        <v>79623</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3086,13 +3082,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>563118</v>
+        <v>563117</v>
       </c>
       <c r="R24" t="n">
-        <v>7061145</v>
+        <v>7061221</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3148,10 +3144,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119839446</v>
+        <v>119839763</v>
       </c>
       <c r="B25" t="n">
-        <v>79607</v>
+        <v>78542</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3164,21 +3160,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3188,13 +3184,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>563109</v>
+        <v>563149</v>
       </c>
       <c r="R25" t="n">
-        <v>7061011</v>
+        <v>7061158</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3238,22 +3234,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119839454</v>
+        <v>119839467</v>
       </c>
       <c r="B26" t="n">
-        <v>79642</v>
+        <v>97930</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3262,38 +3258,42 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>563112</v>
+        <v>563127</v>
       </c>
       <c r="R26" t="n">
-        <v>7061002</v>
+        <v>7061031</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3323,9 +3323,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3340,22 +3350,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119839763</v>
+        <v>119840078</v>
       </c>
       <c r="B27" t="n">
-        <v>78526</v>
+        <v>79623</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3368,21 +3378,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3392,13 +3402,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>563149</v>
+        <v>563078</v>
       </c>
       <c r="R27" t="n">
-        <v>7061158</v>
+        <v>7061270</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3442,22 +3452,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119839930</v>
+        <v>119839817</v>
       </c>
       <c r="B28" t="n">
-        <v>78526</v>
+        <v>79623</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3470,37 +3480,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>563131</v>
+        <v>563119</v>
       </c>
       <c r="R28" t="n">
-        <v>7061213</v>
+        <v>7061134</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3527,19 +3537,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>18:57</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>18:57</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3554,22 +3554,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119839817</v>
+        <v>119839461</v>
       </c>
       <c r="B29" t="n">
-        <v>79607</v>
+        <v>79659</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3578,25 +3578,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3606,13 +3606,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>563119</v>
+        <v>563111</v>
       </c>
       <c r="R29" t="n">
-        <v>7061134</v>
+        <v>7061002</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3668,10 +3668,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119840075</v>
+        <v>119840180</v>
       </c>
       <c r="B30" t="n">
-        <v>57310</v>
+        <v>78542</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3684,21 +3684,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3708,10 +3708,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>563082</v>
+        <v>563031</v>
       </c>
       <c r="R30" t="n">
-        <v>7061251</v>
+        <v>7061307</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3753,12 +3753,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>19:04</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3785,10 +3780,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119839765</v>
+        <v>119839346</v>
       </c>
       <c r="B31" t="n">
-        <v>78526</v>
+        <v>79652</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3797,41 +3792,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>563109</v>
+        <v>563107</v>
       </c>
       <c r="R31" t="n">
-        <v>7061135</v>
+        <v>7061023</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3858,14 +3853,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På tall</t>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3880,12 +3880,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>

--- a/artfynd/A 38185-2024 artfynd.xlsx
+++ b/artfynd/A 38185-2024 artfynd.xlsx
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119839750</v>
+        <v>119840005</v>
       </c>
       <c r="B8" t="n">
-        <v>78542</v>
+        <v>79658</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,20 +1323,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1347,17 +1347,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563142</v>
+        <v>563121</v>
       </c>
       <c r="R8" t="n">
-        <v>7061132</v>
+        <v>7061221</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1384,19 +1384,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>18:48</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>18:48</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1411,22 +1401,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119839784</v>
+        <v>119840152</v>
       </c>
       <c r="B9" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1439,34 +1429,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563118</v>
+        <v>563083</v>
       </c>
       <c r="R9" t="n">
-        <v>7061145</v>
+        <v>7061265</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,9 +1486,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1513,22 +1518,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119839630</v>
+        <v>119839438</v>
       </c>
       <c r="B10" t="n">
-        <v>57473</v>
+        <v>79624</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1541,46 +1546,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563124</v>
+        <v>563107</v>
       </c>
       <c r="R10" t="n">
-        <v>7061062</v>
+        <v>7061010</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1607,19 +1603,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>18:44</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>18:44</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1634,22 +1620,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119839438</v>
+        <v>119839467</v>
       </c>
       <c r="B11" t="n">
-        <v>79624</v>
+        <v>97930</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1658,41 +1644,45 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563107</v>
+        <v>563127</v>
       </c>
       <c r="R11" t="n">
-        <v>7061010</v>
+        <v>7061031</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1719,9 +1709,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1736,22 +1736,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119839454</v>
+        <v>119839784</v>
       </c>
       <c r="B12" t="n">
-        <v>79658</v>
+        <v>79623</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1760,25 +1760,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563112</v>
+        <v>563118</v>
       </c>
       <c r="R12" t="n">
-        <v>7061002</v>
+        <v>7061145</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1850,10 +1850,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119840005</v>
+        <v>119839930</v>
       </c>
       <c r="B13" t="n">
-        <v>79658</v>
+        <v>78542</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1862,20 +1862,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1886,17 +1886,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563121</v>
+        <v>563131</v>
       </c>
       <c r="R13" t="n">
-        <v>7061221</v>
+        <v>7061213</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1923,9 +1923,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>18:57</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1940,22 +1950,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119839930</v>
+        <v>119839788</v>
       </c>
       <c r="B14" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1968,37 +1978,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>563131</v>
+        <v>563157</v>
       </c>
       <c r="R14" t="n">
-        <v>7061213</v>
+        <v>7061169</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2025,19 +2035,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>18:57</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>18:57</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2052,19 +2052,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119839765</v>
+        <v>119839436</v>
       </c>
       <c r="B15" t="n">
         <v>78542</v>
@@ -2100,17 +2100,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563109</v>
+        <v>563131</v>
       </c>
       <c r="R15" t="n">
-        <v>7061135</v>
+        <v>7061038</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2137,14 +2137,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>18:38</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På tall</t>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2159,22 +2164,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119839492</v>
+        <v>119839272</v>
       </c>
       <c r="B16" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2187,37 +2192,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>563115</v>
+        <v>563107</v>
       </c>
       <c r="R16" t="n">
-        <v>7061068</v>
+        <v>7061023</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2244,14 +2249,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>18:33</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2266,19 +2276,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119839272</v>
+        <v>119839765</v>
       </c>
       <c r="B17" t="n">
         <v>78542</v>
@@ -2314,17 +2324,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>563107</v>
+        <v>563109</v>
       </c>
       <c r="R17" t="n">
-        <v>7061023</v>
+        <v>7061135</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2351,19 +2361,14 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>18:33</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>18:33</t>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2378,12 +2383,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2492,7 +2497,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119840075</v>
+        <v>119839492</v>
       </c>
       <c r="B19" t="n">
         <v>57320</v>
@@ -2528,17 +2533,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>563082</v>
+        <v>563115</v>
       </c>
       <c r="R19" t="n">
-        <v>7061251</v>
+        <v>7061068</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2565,19 +2570,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>19:04</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>19:04</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2597,22 +2592,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119840152</v>
+        <v>119839630</v>
       </c>
       <c r="B20" t="n">
-        <v>57320</v>
+        <v>57473</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2625,34 +2620,43 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>563083</v>
+        <v>563124</v>
       </c>
       <c r="R20" t="n">
-        <v>7061265</v>
+        <v>7061062</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2684,7 +2688,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2694,12 +2698,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>19:05</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2726,10 +2725,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119839436</v>
+        <v>119839998</v>
       </c>
       <c r="B21" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2742,37 +2741,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>563131</v>
+        <v>563117</v>
       </c>
       <c r="R21" t="n">
-        <v>7061038</v>
+        <v>7061221</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2799,19 +2798,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>18:38</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>18:38</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2826,22 +2815,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119840035</v>
+        <v>119839750</v>
       </c>
       <c r="B22" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2854,37 +2843,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>563084</v>
+        <v>563142</v>
       </c>
       <c r="R22" t="n">
-        <v>7061225</v>
+        <v>7061132</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2911,9 +2900,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>18:48</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2928,19 +2927,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119839788</v>
+        <v>119840035</v>
       </c>
       <c r="B23" t="n">
         <v>79623</v>
@@ -2980,10 +2979,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>563157</v>
+        <v>563084</v>
       </c>
       <c r="R23" t="n">
-        <v>7061169</v>
+        <v>7061225</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3030,22 +3029,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119839998</v>
+        <v>119839346</v>
       </c>
       <c r="B24" t="n">
-        <v>79623</v>
+        <v>79652</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3054,41 +3053,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>563117</v>
+        <v>563107</v>
       </c>
       <c r="R24" t="n">
-        <v>7061221</v>
+        <v>7061023</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3115,9 +3114,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3132,12 +3141,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3246,10 +3255,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119839467</v>
+        <v>119840180</v>
       </c>
       <c r="B26" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3258,42 +3267,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>563127</v>
+        <v>563031</v>
       </c>
       <c r="R26" t="n">
-        <v>7061031</v>
+        <v>7061307</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3325,7 +3330,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3335,7 +3340,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3362,7 +3367,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119840078</v>
+        <v>119839817</v>
       </c>
       <c r="B27" t="n">
         <v>79623</v>
@@ -3402,13 +3407,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>563078</v>
+        <v>563119</v>
       </c>
       <c r="R27" t="n">
-        <v>7061270</v>
+        <v>7061134</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3464,7 +3469,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119839817</v>
+        <v>119840078</v>
       </c>
       <c r="B28" t="n">
         <v>79623</v>
@@ -3504,13 +3509,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>563119</v>
+        <v>563078</v>
       </c>
       <c r="R28" t="n">
-        <v>7061134</v>
+        <v>7061270</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3566,10 +3571,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119839461</v>
+        <v>119840075</v>
       </c>
       <c r="B29" t="n">
-        <v>79659</v>
+        <v>57320</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3578,38 +3583,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>563111</v>
+        <v>563082</v>
       </c>
       <c r="R29" t="n">
-        <v>7061002</v>
+        <v>7061251</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3639,9 +3644,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>19:04</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>19:04</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3656,22 +3676,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119840180</v>
+        <v>119839454</v>
       </c>
       <c r="B30" t="n">
-        <v>78542</v>
+        <v>79658</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3680,20 +3700,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3704,14 +3724,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>563031</v>
+        <v>563112</v>
       </c>
       <c r="R30" t="n">
-        <v>7061307</v>
+        <v>7061002</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3741,19 +3761,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>19:08</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>19:08</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3768,22 +3778,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119839346</v>
+        <v>119839461</v>
       </c>
       <c r="B31" t="n">
-        <v>79652</v>
+        <v>79659</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3796,34 +3806,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>563107</v>
+        <v>563111</v>
       </c>
       <c r="R31" t="n">
-        <v>7061023</v>
+        <v>7061002</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3853,19 +3863,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>18:35</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>18:35</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3880,12 +3880,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>

--- a/artfynd/A 38185-2024 artfynd.xlsx
+++ b/artfynd/A 38185-2024 artfynd.xlsx
@@ -1413,10 +1413,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119840152</v>
+        <v>119839438</v>
       </c>
       <c r="B9" t="n">
-        <v>57320</v>
+        <v>79624</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,37 +1429,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563083</v>
+        <v>563107</v>
       </c>
       <c r="R9" t="n">
-        <v>7061265</v>
+        <v>7061010</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1486,24 +1486,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>19:05</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>19:05</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1518,22 +1503,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119839438</v>
+        <v>119840152</v>
       </c>
       <c r="B10" t="n">
-        <v>79624</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1546,37 +1531,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563107</v>
+        <v>563083</v>
       </c>
       <c r="R10" t="n">
-        <v>7061010</v>
+        <v>7061265</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1603,9 +1588,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1620,12 +1620,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -2604,10 +2604,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119839630</v>
+        <v>119839998</v>
       </c>
       <c r="B20" t="n">
-        <v>57473</v>
+        <v>79623</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2620,46 +2620,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>563124</v>
+        <v>563117</v>
       </c>
       <c r="R20" t="n">
-        <v>7061062</v>
+        <v>7061221</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2686,19 +2677,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>18:44</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>18:44</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2713,22 +2694,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119839998</v>
+        <v>119839630</v>
       </c>
       <c r="B21" t="n">
-        <v>79623</v>
+        <v>57473</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2741,37 +2722,46 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>563117</v>
+        <v>563124</v>
       </c>
       <c r="R21" t="n">
-        <v>7061221</v>
+        <v>7061062</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2798,9 +2788,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>18:44</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,12 +2815,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3041,10 +3041,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119839346</v>
+        <v>119839763</v>
       </c>
       <c r="B24" t="n">
-        <v>79652</v>
+        <v>78542</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3053,41 +3053,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>563107</v>
+        <v>563149</v>
       </c>
       <c r="R24" t="n">
-        <v>7061023</v>
+        <v>7061158</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3114,19 +3114,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>18:35</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>18:35</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3141,22 +3131,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119839763</v>
+        <v>119839346</v>
       </c>
       <c r="B25" t="n">
-        <v>78542</v>
+        <v>79652</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3165,41 +3155,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>563149</v>
+        <v>563107</v>
       </c>
       <c r="R25" t="n">
-        <v>7061158</v>
+        <v>7061023</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3226,9 +3216,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3243,12 +3243,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>

--- a/artfynd/A 38185-2024 artfynd.xlsx
+++ b/artfynd/A 38185-2024 artfynd.xlsx
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119840005</v>
+        <v>119840152</v>
       </c>
       <c r="B8" t="n">
-        <v>79658</v>
+        <v>57320</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,41 +1323,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563121</v>
+        <v>563083</v>
       </c>
       <c r="R8" t="n">
-        <v>7061221</v>
+        <v>7061265</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1384,9 +1384,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1401,22 +1416,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119839438</v>
+        <v>119840180</v>
       </c>
       <c r="B9" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,37 +1444,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563107</v>
+        <v>563031</v>
       </c>
       <c r="R9" t="n">
-        <v>7061010</v>
+        <v>7061307</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1486,9 +1501,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>19:08</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1503,22 +1528,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119840152</v>
+        <v>119839446</v>
       </c>
       <c r="B10" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1531,34 +1556,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563083</v>
+        <v>563109</v>
       </c>
       <c r="R10" t="n">
-        <v>7061265</v>
+        <v>7061011</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1588,24 +1613,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>19:05</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>19:05</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1620,22 +1630,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119839467</v>
+        <v>119839930</v>
       </c>
       <c r="B11" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1644,42 +1654,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563127</v>
+        <v>563131</v>
       </c>
       <c r="R11" t="n">
-        <v>7061031</v>
+        <v>7061213</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1711,7 +1717,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1721,7 +1727,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1748,10 +1754,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119839784</v>
+        <v>119839272</v>
       </c>
       <c r="B12" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1764,34 +1770,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563118</v>
+        <v>563107</v>
       </c>
       <c r="R12" t="n">
-        <v>7061145</v>
+        <v>7061023</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1821,9 +1827,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>18:33</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1838,19 +1854,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119839930</v>
+        <v>119839763</v>
       </c>
       <c r="B13" t="n">
         <v>78542</v>
@@ -1886,17 +1902,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563131</v>
+        <v>563149</v>
       </c>
       <c r="R13" t="n">
-        <v>7061213</v>
+        <v>7061158</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1923,19 +1939,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>18:57</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>18:57</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1950,22 +1956,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119839788</v>
+        <v>119839438</v>
       </c>
       <c r="B14" t="n">
-        <v>79623</v>
+        <v>79624</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1978,21 +1984,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2002,10 +2008,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>563157</v>
+        <v>563107</v>
       </c>
       <c r="R14" t="n">
-        <v>7061169</v>
+        <v>7061010</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2052,22 +2058,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119839436</v>
+        <v>119839346</v>
       </c>
       <c r="B15" t="n">
-        <v>78542</v>
+        <v>79652</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2076,25 +2082,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2104,10 +2110,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563131</v>
+        <v>563107</v>
       </c>
       <c r="R15" t="n">
-        <v>7061038</v>
+        <v>7061023</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2139,7 +2145,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2149,7 +2155,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2176,10 +2182,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119839272</v>
+        <v>119840005</v>
       </c>
       <c r="B16" t="n">
-        <v>78542</v>
+        <v>79658</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2188,20 +2194,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2212,17 +2218,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>563107</v>
+        <v>563121</v>
       </c>
       <c r="R16" t="n">
-        <v>7061023</v>
+        <v>7061221</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2249,19 +2255,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>18:33</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>18:33</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2276,22 +2272,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119839765</v>
+        <v>119839788</v>
       </c>
       <c r="B17" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2304,21 +2300,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2328,10 +2324,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>563109</v>
+        <v>563157</v>
       </c>
       <c r="R17" t="n">
-        <v>7061135</v>
+        <v>7061169</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2366,11 +2362,6 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På tall</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2383,22 +2374,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119839446</v>
+        <v>119840075</v>
       </c>
       <c r="B18" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2411,34 +2402,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>563109</v>
+        <v>563082</v>
       </c>
       <c r="R18" t="n">
-        <v>7061011</v>
+        <v>7061251</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2468,9 +2459,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>19:04</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>19:04</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2485,22 +2491,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119839492</v>
+        <v>119839784</v>
       </c>
       <c r="B19" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2513,21 +2519,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2537,13 +2543,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>563115</v>
+        <v>563118</v>
       </c>
       <c r="R19" t="n">
-        <v>7061068</v>
+        <v>7061145</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2573,11 +2579,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2592,22 +2593,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119839998</v>
+        <v>119839765</v>
       </c>
       <c r="B20" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2620,21 +2621,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2644,10 +2645,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>563117</v>
+        <v>563109</v>
       </c>
       <c r="R20" t="n">
-        <v>7061221</v>
+        <v>7061135</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2680,6 +2681,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2706,10 +2712,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119839630</v>
+        <v>119839492</v>
       </c>
       <c r="B21" t="n">
-        <v>57473</v>
+        <v>57320</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2722,46 +2728,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>563124</v>
+        <v>563115</v>
       </c>
       <c r="R21" t="n">
-        <v>7061062</v>
+        <v>7061068</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2788,19 +2785,14 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>18:44</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>18:44</t>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,22 +2807,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119839750</v>
+        <v>119840035</v>
       </c>
       <c r="B22" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2843,37 +2835,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>563142</v>
+        <v>563084</v>
       </c>
       <c r="R22" t="n">
-        <v>7061132</v>
+        <v>7061225</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2900,19 +2892,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>18:48</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>18:48</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2927,22 +2909,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119840035</v>
+        <v>119839630</v>
       </c>
       <c r="B23" t="n">
-        <v>79623</v>
+        <v>57473</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2955,37 +2937,46 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>563084</v>
+        <v>563124</v>
       </c>
       <c r="R23" t="n">
-        <v>7061225</v>
+        <v>7061062</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3012,9 +3003,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>18:44</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3029,22 +3030,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119839763</v>
+        <v>119839467</v>
       </c>
       <c r="B24" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3053,41 +3054,45 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>563149</v>
+        <v>563127</v>
       </c>
       <c r="R24" t="n">
-        <v>7061158</v>
+        <v>7061031</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3114,9 +3119,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3131,22 +3146,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119839346</v>
+        <v>119840078</v>
       </c>
       <c r="B25" t="n">
-        <v>79652</v>
+        <v>79623</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3155,38 +3170,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>563107</v>
+        <v>563078</v>
       </c>
       <c r="R25" t="n">
-        <v>7061023</v>
+        <v>7061270</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3216,19 +3231,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>18:35</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>18:35</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3243,19 +3248,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119840180</v>
+        <v>119839436</v>
       </c>
       <c r="B26" t="n">
         <v>78542</v>
@@ -3295,10 +3300,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>563031</v>
+        <v>563131</v>
       </c>
       <c r="R26" t="n">
-        <v>7061307</v>
+        <v>7061038</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3330,7 +3335,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3340,7 +3345,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3367,10 +3372,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119839817</v>
+        <v>119839750</v>
       </c>
       <c r="B27" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3383,37 +3388,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>563119</v>
+        <v>563142</v>
       </c>
       <c r="R27" t="n">
-        <v>7061134</v>
+        <v>7061132</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3440,9 +3445,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>18:48</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3457,19 +3472,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119840078</v>
+        <v>119839817</v>
       </c>
       <c r="B28" t="n">
         <v>79623</v>
@@ -3509,13 +3524,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>563078</v>
+        <v>563119</v>
       </c>
       <c r="R28" t="n">
-        <v>7061270</v>
+        <v>7061134</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3571,10 +3586,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119840075</v>
+        <v>119839454</v>
       </c>
       <c r="B29" t="n">
-        <v>57320</v>
+        <v>79658</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3583,38 +3598,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>563082</v>
+        <v>563112</v>
       </c>
       <c r="R29" t="n">
-        <v>7061251</v>
+        <v>7061002</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3644,24 +3659,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>19:04</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>19:04</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3676,22 +3676,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119839454</v>
+        <v>119839998</v>
       </c>
       <c r="B30" t="n">
-        <v>79658</v>
+        <v>79623</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3700,25 +3700,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3728,13 +3728,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>563112</v>
+        <v>563117</v>
       </c>
       <c r="R30" t="n">
-        <v>7061002</v>
+        <v>7061221</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>

--- a/artfynd/A 38185-2024 artfynd.xlsx
+++ b/artfynd/A 38185-2024 artfynd.xlsx
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119840152</v>
+        <v>119840180</v>
       </c>
       <c r="B8" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563083</v>
+        <v>563031</v>
       </c>
       <c r="R8" t="n">
-        <v>7061265</v>
+        <v>7061307</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1396,12 +1396,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>19:05</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1428,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119840180</v>
+        <v>119840152</v>
       </c>
       <c r="B9" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1444,21 +1439,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1468,10 +1463,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563031</v>
+        <v>563083</v>
       </c>
       <c r="R9" t="n">
-        <v>7061307</v>
+        <v>7061265</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1503,7 +1498,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1513,7 +1508,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2386,10 +2386,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119840075</v>
+        <v>119839765</v>
       </c>
       <c r="B18" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2402,37 +2402,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>563082</v>
+        <v>563109</v>
       </c>
       <c r="R18" t="n">
-        <v>7061251</v>
+        <v>7061135</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2459,24 +2459,14 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>19:04</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>19:04</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2491,12 +2481,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2605,10 +2595,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119839765</v>
+        <v>119840075</v>
       </c>
       <c r="B20" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2621,37 +2611,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>563109</v>
+        <v>563082</v>
       </c>
       <c r="R20" t="n">
-        <v>7061135</v>
+        <v>7061251</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2678,14 +2668,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>19:04</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>19:04</t>
+        </is>
+      </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2700,12 +2700,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
